--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92553948885</v>
+        <v>46157.93108854608</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93108854608</v>
+        <v>46157.93133314511</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93133314511</v>
+        <v>46157.93381213087</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93381213087</v>
+        <v>46157.93692468039</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93692468039</v>
+        <v>46158.28203669513</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28203669513</v>
+        <v>46158.29650162793</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29650162793</v>
+        <v>46158.29804558962</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29804558962</v>
+        <v>46158.33368064009</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33368064009</v>
+        <v>46158.37219932637</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/12. ИП Лопакова Н.Ф. (аренда транспорта)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37219932637</v>
+        <v>46158.37274247387</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
